--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0210.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0210.xlsx
@@ -2004,7 +2004,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>"Vẫn chưa nhớ à? Để ta nói rõ cho. Hệ thống gắn cờ ta vì tội mưu sát Quản gia trưởng Bờ Biển Đen. Giờ thì nhớ ra chưa?"</t>
+          <t>"Vẫn chưa nhớ à? Để tao nói rõ cho. Hệ thống gắn cờ tao vì tội mưu sát Quản gia trưởng Bờ Biển Đen. Giờ thì nhớ ra chưa?"</t>
         </is>
       </c>
     </row>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>"Ta đã thấy cách ngươi xử lý các vụ án hồi xưa. Chính xác. Lưỡi dao sắc, đầu óc cũng sắc. Đủ để ta thấy thú vị."</t>
+          <t>"Tao đã thấy cách mày xử lý các vụ án hồi xưa. Chính xác. Lưỡi dao sắc, đầu óc cũng sắc. Đủ để tao thấy thú vị."</t>
         </is>
       </c>
     </row>
@@ -3176,7 +3176,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Chạy đi... Chạy để sống, có thể cậu sẽ thoát khỏi nơi này mãi mãi.</t>
+          <t>Chạy đi... Chạy để sống, có thể mày sẽ thoát khỏi nơi này mãi mãi.</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>"Ấn tượng đấy! Ta cứ tưởng những câu chuyện về việc ngươi đứng đầu Học viện Sentinel chỉ là phóng đại, nhưng giờ ta thấy mình đã sai."</t>
+          <t>"Ấn tượng đấy! Tao cứ tưởng những câu chuyện về việc mày đứng đầu Học viện Sentinel chỉ là phóng đại, nhưng giờ tao thấy mình đã sai."</t>
         </is>
       </c>
     </row>
@@ -4801,7 +4801,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>"Ngươi nghĩ có thể nhốt ta ở đây sao?"</t>
+          <t>"Mày nghĩ có thể nhốt ta ở đây sao?"</t>
         </is>
       </c>
     </row>
@@ -8376,7 +8376,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>"Hừ... Để ta lo."</t>
+          <t>"Hừ... Để tao lo."</t>
         </is>
       </c>
     </row>
@@ -9806,7 +9806,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>"Sẵn sàng bất cứ lúc nào. Cứ thế này, biết đâu ta lại trở thành nhà phê bình phim chuyên nghiệp mất."</t>
+          <t>"Sẵn sàng bất cứ lúc nào. Cứ thế này, biết đâu tao lại trở thành nhà phê bình phim chuyên nghiệp mất."</t>
         </is>
       </c>
     </row>
@@ -13446,7 +13446,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>"Được rồi, đến một cuộc phiêu lưu mới! Nhưng khoan, sao cậu không đeo cái Huy hiệu Len mà ta tặng, Astral?"</t>
+          <t>"Được rồi, đến một cuộc phiêu lưu mới! Nhưng khoan, sao cậu không đeo cái Huy hiệu Len mà tao tặng, Astral?"</t>
         </is>
       </c>
     </row>
@@ -14488,7 +14488,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>"…Ta từng tin rằng Psyche Pass là hoàn hảo. Với nó, không tội phạm nào có thể thoát khỏi công lý."</t>
+          <t>"…Tao từng tin rằng Psyche Pass là hoàn hảo. Với nó, không tội phạm nào có thể thoát khỏi công lý."</t>
         </is>
       </c>
     </row>
@@ -14553,7 +14553,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>"Nhưng khi lệnh truy nã của ngươi xuất hiện, ta bắt đầu nghi ngờ. Ngươi là người chính trực nhất mà ta—" Hắn ho khan. "Người mà ta biết."</t>
+          <t>"Nhưng khi lệnh truy nã của mày xuất hiện, tao bắt đầu nghi ngờ. Mày là người chính trực nhất mà tao—" Hắn ho khan. "Người mà tao biết."</t>
         </is>
       </c>
     </row>
@@ -15008,7 +15008,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>"Đừng có mà đụng vào hàng hóa của ta!"</t>
+          <t>"Đừng có mà đụng vào hàng hóa của tao!"</t>
         </is>
       </c>
     </row>
@@ -16633,7 +16633,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>"Được rồi! Quyết định vậy nhé! Hoàng tử Cosmos, vũ khí của cậu là Cheese Prescient! Còn Công chúa Cloudy, cậu nhận được Carrot Kiếm! Giờ thì chúng ta đã sẵn sàng cho trận chiến!"</t>
+          <t>"Được rồi! Quyết định vậy nhé! Hoàng tử Cosmos, vũ khí của cậu là Cheese Prescient! Còn Công chúa Cloudy, cậu nhận được Carrot Kiếm đơn! Giờ thì chúng ta đã sẵn sàng cho trận chiến!"</t>
         </is>
       </c>
     </row>
@@ -19103,7 +19103,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>"Nhưng," cậu dừng lại, nhìn thẳng vào hắn. "Cậu có đứng về phe hệ thống không?"</t>
+          <t>"Nhưng," cậu dừng lại, nhìn thẳng vào hắn. "Mày có đứng về phe hệ thống không?"</t>
         </is>
       </c>
     </row>
@@ -19363,7 +19363,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>"Mọi thứ đều có cách giải quyết, và ta sẽ không bị mắc kẹt mãi ở đây đâu." Hắn cười nhếch mép, ánh mắt lấp lánh. "Ta chỉ đang... chờ đúng thời điểm thôi."</t>
+          <t>"Mọi thứ đều có cách giải quyết, và tao sẽ không bị mắc kẹt mãi ở đây đâu." Hắn cười nhếch mép, ánh mắt lấp lánh. "Tao chỉ đang... chờ đúng thời điểm thôi."</t>
         </is>
       </c>
     </row>
@@ -20338,7 +20338,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Bản năng mách bảo cậu bước vào tòa nhà này.</t>
+          <t>Bản năng mách bảo bạn bước vào tòa nhà này.</t>
         </is>
       </c>
     </row>
@@ -21118,7 +21118,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>Bản năng mách bảo cậu bước vào tòa nhà này.</t>
+          <t>Bản năng mách bảo bạn bước vào tòa nhà này.</t>
         </is>
       </c>
     </row>
@@ -26848,7 +26848,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>"Ta ổn."</t>
+          <t>"Tao ổn."</t>
         </is>
       </c>
     </row>
